--- a/main/ig/ValueSet-fr-doc-vs-participation-type-participant.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type-participant.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
